--- a/rifa/numeros.xlsx
+++ b/rifa/numeros.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\user usuario\rifa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Datos\Escritorio\03 03 26\Downloads\rifa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00F40728-0C19-4E1F-BAF0-44218E7690A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46076F9B-78BD-408C-84B8-4EC96291A5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{4B9B74DE-FA6A-450F-A61A-00FAA1B84507}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Numero de rifa</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>Juan</t>
+  </si>
+  <si>
+    <t>Maria</t>
   </si>
 </sst>
 </file>
@@ -464,6 +467,9 @@
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">

--- a/rifa/numeros.xlsx
+++ b/rifa/numeros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Datos\Escritorio\03 03 26\Downloads\rifa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46076F9B-78BD-408C-84B8-4EC96291A5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1314CC04-A77F-49D4-87C3-595E70D9EAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{4B9B74DE-FA6A-450F-A61A-00FAA1B84507}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Numero de rifa</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Juan</t>
-  </si>
-  <si>
-    <t>Maria</t>
   </si>
 </sst>
 </file>
@@ -467,9 +464,6 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">

--- a/rifa/numeros.xlsx
+++ b/rifa/numeros.xlsx
@@ -1,64 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Datos\Escritorio\03 03 26\Downloads\rifa\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1314CC04-A77F-49D4-87C3-595E70D9EAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{4B9B74DE-FA6A-450F-A61A-00FAA1B84507}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Numero de rifa</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Juan</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -84,21 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -113,44 +86,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -178,31 +151,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -230,23 +186,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -258,136 +197,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -409,281 +392,824 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44262693-2A0D-48B5-837B-4FC45AEFF1B6}">
-  <dimension ref="A1:B51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B101"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Numero de rifa</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Nombre</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="str">
+        <v>Juan</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15">
         <v>14</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28">
         <v>27</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29">
         <v>28</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31">
         <v>30</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32">
         <v>31</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33">
         <v>32</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34">
         <v>33</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36">
         <v>35</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44">
         <v>43</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45">
         <v>44</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47">
         <v>46</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48">
         <v>47</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49">
         <v>48</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50">
         <v>49</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51">
         <v>50</v>
       </c>
+      <c r="B51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B101"/>
+  </ignoredErrors>
 </worksheet>
 </file>